--- a/manuscript/Analisis_y_Auditoria/Acumulacion_Taxones.xlsx
+++ b/manuscript/Analisis_y_Auditoria/Acumulacion_Taxones.xlsx
@@ -399,10 +399,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>5.771771771771772</v>
+        <v>5.86986986986987</v>
       </c>
       <c r="D2">
-        <v>2.025875689320825</v>
+        <v>2.070182212238048</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -413,10 +413,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>9.497497497497497</v>
+        <v>9.42942942942943</v>
       </c>
       <c r="D3">
-        <v>2.559853402566054</v>
+        <v>2.536857518054294</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -427,10 +427,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>12.41341341341341</v>
+        <v>12.41941941941942</v>
       </c>
       <c r="D4">
-        <v>2.787436072806015</v>
+        <v>2.760163086448126</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -441,10 +441,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>14.90690690690691</v>
+        <v>14.8998998998999</v>
       </c>
       <c r="D5">
-        <v>2.813569741756154</v>
+        <v>2.898411905360634</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -455,10 +455,10 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>16.96996996996997</v>
+        <v>17.01101101101101</v>
       </c>
       <c r="D6">
-        <v>2.804072885749636</v>
+        <v>2.828228532516983</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -469,10 +469,10 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>18.82982982982983</v>
+        <v>18.81781781781782</v>
       </c>
       <c r="D7">
-        <v>2.669329824974814</v>
+        <v>2.655738831346842</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -483,10 +483,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>20.48048048048048</v>
+        <v>20.48948948948949</v>
       </c>
       <c r="D8">
-        <v>2.487114965390927</v>
+        <v>2.453503413006575</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -497,10 +497,10 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>21.8958958958959</v>
+        <v>21.88288288288288</v>
       </c>
       <c r="D9">
-        <v>2.248395814943286</v>
+        <v>2.252430728273044</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -511,10 +511,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>23.14014014014014</v>
+        <v>23.1971971971972</v>
       </c>
       <c r="D10">
-        <v>1.999594242502633</v>
+        <v>1.966694670763148</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -525,10 +525,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>24.33733733733734</v>
+        <v>24.35635635635636</v>
       </c>
       <c r="D11">
-        <v>1.666995821066214</v>
+        <v>1.651845733047949</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -539,10 +539,10 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>25.2982982982983</v>
+        <v>25.31031031031031</v>
       </c>
       <c r="D12">
-        <v>1.323862655931743</v>
+        <v>1.325638880195196</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -553,10 +553,10 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>26.26326326326326</v>
+        <v>26.22722722722723</v>
       </c>
       <c r="D13">
-        <v>0.8679103054800529</v>
+        <v>0.8994651157261386</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,10 +581,10 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>7.271271271271272</v>
+        <v>7.069069069069069</v>
       </c>
       <c r="D15">
-        <v>2.009368210831176</v>
+        <v>1.999557624982457</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -595,10 +595,10 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>12.29029029029029</v>
+        <v>12.05505505505506</v>
       </c>
       <c r="D16">
-        <v>2.360287637403199</v>
+        <v>2.436769924984012</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -609,10 +609,10 @@
         <v>3</v>
       </c>
       <c r="C17">
-        <v>16.07307307307307</v>
+        <v>15.86986986986987</v>
       </c>
       <c r="D17">
-        <v>2.416058845797921</v>
+        <v>2.525835063621598</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -623,10 +623,10 @@
         <v>4</v>
       </c>
       <c r="C18">
-        <v>19.10710710710711</v>
+        <v>18.93293293293293</v>
       </c>
       <c r="D18">
-        <v>2.458378895354781</v>
+        <v>2.5678188982666</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -637,10 +637,10 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>21.56956956956957</v>
+        <v>21.40640640640641</v>
       </c>
       <c r="D19">
-        <v>2.551850072496406</v>
+        <v>2.545182686727346</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -651,10 +651,10 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>23.76376376376376</v>
+        <v>23.53353353353353</v>
       </c>
       <c r="D20">
-        <v>2.576339126520017</v>
+        <v>2.575245698460927</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -665,10 +665,10 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>25.54554554554555</v>
+        <v>25.32932932932933</v>
       </c>
       <c r="D21">
-        <v>2.512429557667669</v>
+        <v>2.544326599779072</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -679,10 +679,10 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>27.07307307307307</v>
+        <v>26.94394394394394</v>
       </c>
       <c r="D22">
-        <v>2.49722604934931</v>
+        <v>2.528962665835786</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -693,10 +693,10 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>28.45445445445445</v>
+        <v>28.34134134134134</v>
       </c>
       <c r="D23">
-        <v>2.433417497906167</v>
+        <v>2.434431250544953</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -707,10 +707,10 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>29.67367367367367</v>
+        <v>29.48448448448448</v>
       </c>
       <c r="D24">
-        <v>2.40357482961124</v>
+        <v>2.359798042866326</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -721,10 +721,10 @@
         <v>11</v>
       </c>
       <c r="C25">
-        <v>30.73073073073073</v>
+        <v>30.54254254254254</v>
       </c>
       <c r="D25">
-        <v>2.274844258265892</v>
+        <v>2.255241488240784</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -735,10 +735,10 @@
         <v>12</v>
       </c>
       <c r="C26">
-        <v>31.6976976976977</v>
+        <v>31.57957957957958</v>
       </c>
       <c r="D26">
-        <v>2.147540118793677</v>
+        <v>2.138356509224903</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -749,10 +749,10 @@
         <v>13</v>
       </c>
       <c r="C27">
-        <v>32.57557557557558</v>
+        <v>32.45345345345346</v>
       </c>
       <c r="D27">
-        <v>2.039697225960566</v>
+        <v>1.982788057899958</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -763,10 +763,10 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>33.29129129129129</v>
+        <v>33.27427427427428</v>
       </c>
       <c r="D28">
-        <v>1.96161415533817</v>
+        <v>1.844900040970023</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -777,10 +777,10 @@
         <v>15</v>
       </c>
       <c r="C29">
-        <v>34.06306306306306</v>
+        <v>34.02702702702702</v>
       </c>
       <c r="D29">
-        <v>1.854698584867213</v>
+        <v>1.744234783574371</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -791,10 +791,10 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>34.73873873873874</v>
+        <v>34.67667667667668</v>
       </c>
       <c r="D30">
-        <v>1.680612903161032</v>
+        <v>1.629686572078506</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -805,10 +805,10 @@
         <v>17</v>
       </c>
       <c r="C31">
-        <v>35.42742742742742</v>
+        <v>35.34434434434434</v>
       </c>
       <c r="D31">
-        <v>1.50166523748118</v>
+        <v>1.501350609568347</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -819,10 +819,10 @@
         <v>18</v>
       </c>
       <c r="C32">
-        <v>35.994994994995</v>
+        <v>35.98598598598598</v>
       </c>
       <c r="D32">
-        <v>1.347816082170594</v>
+        <v>1.316537255261996</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -833,10 +833,10 @@
         <v>19</v>
       </c>
       <c r="C33">
-        <v>36.53753753753754</v>
+        <v>36.56356356356356</v>
       </c>
       <c r="D33">
-        <v>1.119306945578013</v>
+        <v>1.156888280994807</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -847,10 +847,10 @@
         <v>20</v>
       </c>
       <c r="C34">
-        <v>37.04704704704704</v>
+        <v>37.05905905905906</v>
       </c>
       <c r="D34">
-        <v>0.9222200216463746</v>
+        <v>0.9671537044811951</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -861,10 +861,10 @@
         <v>21</v>
       </c>
       <c r="C35">
-        <v>37.54754754754754</v>
+        <v>37.54254254254254</v>
       </c>
       <c r="D35">
-        <v>0.6544831455944652</v>
+        <v>0.6759109802691763</v>
       </c>
     </row>
     <row r="36" spans="1:4">
